--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-10-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>£1029.48</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d40be995+80021]
-	GetHandleVerifier [0x0x7ff6d40be9f0+80112]
-	(No symbol) [0x0x7ff6d3e4060f]
-	(No symbol) [0x0x7ff6d3e98854]
-	(No symbol) [0x0x7ff6d3e98b1c]
-	(No symbol) [0x0x7ff6d3eec927]
-	(No symbol) [0x0x7ff6d3ec126f]
-	(No symbol) [0x0x7ff6d3ee968a]
-	(No symbol) [0x0x7ff6d3ec1003]
-	(No symbol) [0x0x7ff6d3e895d1]
-	(No symbol) [0x0x7ff6d3e8a3f3]
-	GetHandleVerifier [0x0x7ff6d437dd4d+2960461]
-	GetHandleVerifier [0x0x7ff6d437800a+2936586]
-	GetHandleVerifier [0x0x7ff6d4398a47+3070279]
-	GetHandleVerifier [0x0x7ff6d40d847e+185214]
-	GetHandleVerifier [0x0x7ff6d40dfecf+216527]
-	GetHandleVerifier [0x0x7ff6d40c7bd4+117460]
-	GetHandleVerifier [0x0x7ff6d40c7d8f+117903]
-	GetHandleVerifier [0x0x7ff6d40adc68+11112]
+	GetHandleVerifier [0x0x7ff64f61e995+80021]
+	GetHandleVerifier [0x0x7ff64f61e9f0+80112]
+	(No symbol) [0x0x7ff64f3a060f]
+	(No symbol) [0x0x7ff64f3f8854]
+	(No symbol) [0x0x7ff64f3f8b1c]
+	(No symbol) [0x0x7ff64f44c927]
+	(No symbol) [0x0x7ff64f42126f]
+	(No symbol) [0x0x7ff64f44968a]
+	(No symbol) [0x0x7ff64f421003]
+	(No symbol) [0x0x7ff64f3e95d1]
+	(No symbol) [0x0x7ff64f3ea3f3]
+	GetHandleVerifier [0x0x7ff64f8ddd4d+2960461]
+	GetHandleVerifier [0x0x7ff64f8d800a+2936586]
+	GetHandleVerifier [0x0x7ff64f8f8a47+3070279]
+	GetHandleVerifier [0x0x7ff64f63847e+185214]
+	GetHandleVerifier [0x0x7ff64f63fecf+216527]
+	GetHandleVerifier [0x0x7ff64f627bd4+117460]
+	GetHandleVerifier [0x0x7ff64f627d8f+117903]
+	GetHandleVerifier [0x0x7ff64f60dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1173.76</t>
+          <t>£1162.4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1296.16</t>
+          <t>£1255.2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
